--- a/Doku/Nutzwertanalyse Enwicklungsbeginn .xlsx
+++ b/Doku/Nutzwertanalyse Enwicklungsbeginn .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonasmuhlbach/Programs_VB/Spiel_1.0/Doku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FCFBA7-67FB-6E46-B6F5-A8CC17B9D4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF673EA-1A98-F044-AA2F-AD6FBEDBC485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Kriterien:</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>NUTZWERT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Ablauf Nutzwertanalyse: 
@@ -155,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -192,17 +189,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -215,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -242,16 +228,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -260,7 +243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -562,47 +545,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="23"/>
-      <c r="B2" s="25"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" s="22"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -615,26 +598,26 @@
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5">
         <v>20</v>
@@ -653,11 +636,11 @@
         <f>B3*E3</f>
         <v>140</v>
       </c>
-      <c r="G3" s="18"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5">
         <v>10</v>
@@ -666,21 +649,21 @@
         <v>8</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" ref="D4:D18" si="0">B4*C4</f>
+        <f t="shared" ref="D4:D8" si="0">B4*C4</f>
         <v>80</v>
       </c>
       <c r="E4" s="2">
         <v>6</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" ref="F4:F18" si="1">B4*E4</f>
+        <f t="shared" ref="F4:F8" si="1">B4*E4</f>
         <v>60</v>
       </c>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5">
         <v>30</v>
@@ -699,11 +682,11 @@
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5">
         <v>20</v>
@@ -722,11 +705,11 @@
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5">
         <v>10</v>
@@ -745,11 +728,11 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5">
         <v>10</v>
@@ -768,273 +751,101 @@
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="5">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="5">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
+        <f>SUM(D3:D8)</f>
+        <v>470</v>
+      </c>
+      <c r="F9" s="3">
+        <f>SUM(F3:F8)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="112.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="L10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="W10" s="11"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="3">
-        <f>SUM(D3:D18)</f>
-        <v>470</v>
-      </c>
-      <c r="F19" s="3">
-        <f>SUM(F3:F18)</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="112.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="L20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="W20" s="11"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="N21" s="14"/>
-      <c r="W21" s="11"/>
-    </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="N11" s="13"/>
+      <c r="W11" s="11"/>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1042,7 +853,7 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A21:D29"/>
+    <mergeCell ref="A11:D19"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
